--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127466011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>593132</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6984597</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127466011</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127466011</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127466011</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127466011</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111363002</v>
       </c>
       <c r="B2" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593206.2569888401</v>
+        <v>593206</v>
       </c>
       <c r="R2" t="n">
-        <v>6984597.362029305</v>
+        <v>6984598</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-08-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,11 +775,11 @@
         <v>127466011</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111363002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127466011</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127466011</v>
+        <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödingen, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593132</v>
+        <v>593139</v>
       </c>
       <c r="R3" t="n">
-        <v>6984597</v>
+        <v>6984623</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,22 +863,1162 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135581509</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127466011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593132</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6984597</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127466011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135581503</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593078</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984545</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581503</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135581506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593106</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581506</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135581514</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593145</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984542</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581514</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135581504</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581504</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135581508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593124</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984633</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581508</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135581511</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581511</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135581507</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593119</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984618</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581507</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135581512</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593129</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6984569</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581512</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135581510</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>593136</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6984628</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581510</t>
         </is>
       </c>
     </row>
@@ -886,6 +2026,16 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135581503</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135581506</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135581514</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135581504</v>
       </c>
       <c r="B8" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135581508</v>
       </c>
       <c r="B9" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135581511</v>
       </c>
       <c r="B10" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>135581507</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135581512</v>
       </c>
       <c r="B12" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>135581510</v>
       </c>
       <c r="B13" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135581503</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135581506</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135581514</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135581504</v>
       </c>
       <c r="B8" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135581508</v>
       </c>
       <c r="B9" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135581511</v>
       </c>
       <c r="B10" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>135581507</v>
       </c>
       <c r="B11" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135581512</v>
       </c>
       <c r="B12" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>135581510</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127466011</v>
+        <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödingen, Jmt</t>
+          <t>Ödingen, Bispgården, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593132</v>
+        <v>593139</v>
       </c>
       <c r="R3" t="n">
-        <v>6984597</v>
+        <v>6984623</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,22 +863,1162 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135581509</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127466011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593132</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6984597</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127466011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135581503</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593078</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984545</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581503</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135581506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593106</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984616</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581506</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135581514</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593145</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984542</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581514</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135581504</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984550</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581504</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135581508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593124</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984633</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581508</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135581511</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581511</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135581507</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593119</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984618</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581507</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135581512</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593129</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6984569</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581512</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135581510</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ödingen, Bispgården, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>593136</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6984628</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135581510</t>
         </is>
       </c>
     </row>
@@ -886,6 +2026,16 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135581503</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135581506</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135581514</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135581504</v>
       </c>
       <c r="B8" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135581508</v>
       </c>
       <c r="B9" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135581511</v>
       </c>
       <c r="B10" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>135581507</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135581512</v>
       </c>
       <c r="B12" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>135581510</v>
       </c>
       <c r="B13" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31960-2025 artfynd.xlsx
+++ b/artfynd/A 31960-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135581509</v>
       </c>
       <c r="B3" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135581503</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135581506</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135581514</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135581504</v>
       </c>
       <c r="B8" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135581508</v>
       </c>
       <c r="B9" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135581511</v>
       </c>
       <c r="B10" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>135581507</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135581512</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>135581510</v>
       </c>
       <c r="B13" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
